--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD8F4A0-E891-4D85-AFF5-D26ACC2A8FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C411590E-4769-44C4-ABA7-6A815FB792F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="231">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1014,6 +1014,14 @@
   </si>
   <si>
     <t>在卷积64系数小块内融合Karatsuba三乘法，优化z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H74.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fibonacci倍增直接构造半核，mak降为O(n)，并优化gen核构造</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1446,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3268,6 +3276,23 @@
         <v>228</v>
       </c>
     </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C411590E-4769-44C4-ABA7-6A815FB792F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BBDB56-DC5A-4198-A157-2659F69C68F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="233">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1022,6 +1022,14 @@
   </si>
   <si>
     <t>Fibonacci倍增直接构造半核，mak降为O(n)，并优化gen核构造</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H75.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一了 A/B 的乘法叶节点、核分块和累加核公式。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1454,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3293,6 +3301,23 @@
         <v>230</v>
       </c>
     </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BBDB56-DC5A-4198-A157-2659F69C68F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7AB04B-1B49-48EB-A0B7-BEBBDD3A8921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="235">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1029,7 +1029,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>统一了 A/B 的乘法叶节点、核分块和累加核公式。</t>
+    <t>diandeng10_a_faster2_png_H76.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一AB乘法叶节点、核分块及累加核公式，优化A版z/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定因子预计算16项四位倍式表，优化x，并减少mak冗余操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1462,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3315,7 +3323,24 @@
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
         <v>232</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/_diandeng版本说明.xlsx
+++ b/_diandeng版本说明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Program Files\First Publisher\bin\i386-win32\pas\数学问题\diandeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7AB04B-1B49-48EB-A0B7-BEBBDD3A8921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7769673E-7A22-407B-BB69-7D747D056372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24420" windowHeight="11040" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{24EFE09E-F6DB-4F7F-8F77-51F0A2935513}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="239">
   <si>
     <t>O(n³)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1038,6 +1038,22 @@
   </si>
   <si>
     <t>固定因子预计算16项四位倍式表，优化x，并减少mak冗余操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合128系数小核并复用于普通及成对乘法，优化q/z/x/gen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H77.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diandeng10_a_faster2_png_H78.pas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三分块六乘法减少非二次幂小块的乘法次数，优化q/z/gen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1470,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{444DD116-1455-4CF9-984E-22B77D122286}">
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultColWidth="36.375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
@@ -3343,6 +3359,40 @@
         <v>234</v>
       </c>
     </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
